--- a/pensum/ol20/OL20_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol20/OL20_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="172">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 20: Noen viktige lover (V5)</t>
   </si>
@@ -158,9 +158,18 @@
     <t xml:space="preserve">a)  Hva er det høyeste Nordlys kan kreve for oppdraget etter håndverkertjenesteloven § 32 andre ledd? Regn prisoverslaget pluss 15 prosent.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håndverkertjenesteloven § 32 andre ledd: er det gitt prisoverslag, skal prisen ikke overstige det oppgitte beløpet vesentlig, og i alle fall ikke med mer enn 15 prosent (Organisasjon og ledelse 20.2.4). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange prosent over prisoverslaget ligger fakturaen? Regn overskridelsen i kroner og del på prisoverslaget, ikke på fakturaen. Én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Overskridelse i prosent = (faktura − overslag) / overslag × 100. Grensen er § 32 andre ledd (Organisasjon og ledelse 20.2.4). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Montøren så underveis at prisen ville bli mye høyere enn overslaget, men ringte ikke kunden. Hvilken plikt i håndverkertjenesteloven brøt han?   A: § 5 første ledd: utføre tjenesten fagmessig   B: § 7 andre ledd: kontakte forbrukeren når prisen blir betydelig høyere enn hun måtte vente   C: § 32 første ledd: ta gjengs pris   (skriv bokstaven)</t>
   </si>
   <si>
@@ -185,6 +194,24 @@
     <t xml:space="preserve">e)  Kunden vil bare betale 36 000 kr. Hva bør Kari svare kunden, og hvilken rutine bør Nordlys innføre så det ikke skjer igjen? Tre setninger med paragraf.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk §§ 7 og 32 i håndverkertjenesteloven (20.2.2 og 20.2.4) og bokas konklusjon om tydelig pris (20.2.5). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosenten av overslaget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taket er overslaget × 1,15. Overskridelsen i prosent er (faktura − overslag) / overslag, ikke delt på fakturaen. Det som ligger over taket, kan kunden i alle fall avvise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire tiltak, tre paragrafer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§ 3: kan påstanden dokumenteres nå? Åpenbar overdrivelse er lov. § 18: krever trekningen kjøp? § 9: brukes en maktposisjon til å presse kunden?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.1 (markedsføringsloven §§ 3, 9 og 18) og 20.2 (håndverkertjenesteloven §§ 7 og 32). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -242,18 +269,39 @@
     <t xml:space="preserve">a)  Kunde 2 fikk prisoverslag på 15 300 kr. Hva er det høyeste Fjell kan fakturere for selve oppdraget etter § 32 andre ledd?</t>
   </si>
   <si>
+    <t xml:space="preserve">Håndverkertjenesteloven § 32 andre ledd: prisoverslag kan ikke overstiges vesentlig, og i alle fall ikke med mer enn 15 prosent (Organisasjon og ledelse 20.2.4). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hos kunde 1 finner montøren at laderen trenger et nytt vern i sikringsskapet, utenfor oppdraget. Det er praktisk å gjøre det samtidig. Hva skal han gjøre først etter håndverkertjenesteloven?   A: Montere vernet og legge det på fakturaen; det er praktisk å gjøre samtidig   B: Kontakte kunden før han gjør tilleggsarbeidet (§ 9 første ledd)   C: Ingenting; fast pris betyr at alt nødvendig arbeid er inkludert   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Montøren ringer, og kunde 1 sier ja til vernet. Hva kan Fjell fakturere kunde 1 i alt, inkl. mva? Fast pris for oppdraget pluss tilleggsarbeidet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Håndverkertjenesteloven § 33: tilleggsarbeid som er godtgjort ikke var omfattet av oppdraget, og som er utført i samsvar med § 9, kan kreves betalt (Organisasjon og ledelse 20.2.5). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hos kunde 2 tok jobben lengre tid enn Mona regnet med, uten at noe uforutsett dukket opp. Kan Fjell fakturere 17 595 kr fordi det er innenfor 15 %?   A: Ja, 15 % over overslaget er alltid lov   B: Nei, 15 % er et tak; prisen skal ikke overstige overslaget vesentlig, og overskridelsen må kunne begrunnes   C: Nei, et prisoverslag er det samme som fast pris   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hvilken prisform bør Mona bruke i tilbudsmalen for ladeboks med installasjon, og hvordan skal hun formulere den? Ta stilling til kunde 3 også. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk de fire prisformene og bevisbyrden (20.2.4), tilleggsarbeid (§ 9, 20.2.3) og betaling for tilleggsarbeid (§ 33, 20.2.5). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire prisformer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast pris: aldri mer for oppdraget. Høyeste pris: kan bli lavere, ikke høyere. Prisoverslag: tak på 15 %. Prisantydning: friere, men det er håndverkeren som må bevise at det var det.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utenfor oppdraget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeid utenfor oppdraget er tilleggsarbeid (§ 9). Først telefonen, så verktøyet. Sier kunden ja, kan det kreves betalt i tillegg (§ 33), også ved fast pris.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.2.3–20.2.5 (håndverkertjenesteloven §§ 9, 32 og 33). Pakkeprisen bygger på OK07 og MA06. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -329,6 +377,9 @@
     <t xml:space="preserve">a)  Hvor mange måneders oppsigelsestid har Jonas etter arbeidsmiljøloven § 15-3? Regn ansettelsestiden fra august 2020 til mars i budsjettåret 2027.</t>
   </si>
   <si>
+    <t xml:space="preserve">Arbeidsmiljøloven § 15-3: én måned som hovedregel, to måneder etter fem års ansettelse, tre måneder etter ti år. Fristene står ikke i bokas digitale kopi (20.3.12) og er hentet fra Arbeidstilsynet. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Oppsigelsen gis 20. mars, og fristen er to måneder. Hvilken dag er Jonas' siste dag i arbeidsforholdet?   A: 20. mai   B: 31. mai   C: 30. april   (skriv bokstaven)</t>
   </si>
   <si>
@@ -359,6 +410,21 @@
     <t xml:space="preserve">e)  Hvordan sikrer Kari at valget av Jonas er saklig, og hva gjør hun i hvilken rekkefølge før hun skriver oppsigelsen? Tre setninger med paragraf.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk §§ 15-1, 15-4, 15-7 og 15-15 (20.3.11–20.3.19) og lovens ånd mot lovens bokstav (20.6). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telle riktig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ansatt august 2020, sagt opp mars 2027: over fem, under ti år. Fristen løper fra den første i måneden etter oppsigelsen, ikke fra datoen den ble gitt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvilket forhold?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Er grunnen virksomhetens forhold (nedbemanning) eller arbeidstakerens (pliktbrudd)? Advarsel hører til det siste. Drøfting, skriftlighet og omplassering gjelder alltid.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.3.10–20.3.17 (aml. §§ 15-1, 15-4, 15-5, 15-7, 15-11 og 15-12). Oppsigelsesfristene (§ 15-3) mangler i bokas digitale kopi og er hentet fra Arbeidstilsynet, «Oppsigelse» (hentet 26.09.2026). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -422,12 +488,21 @@
     <t xml:space="preserve">a)  Montøren begynte 1. august, og avtalen ble signert 20. august. Fristen er sju dager etter oppstart. Hvor mange dager for sent ble avtalen signert?</t>
   </si>
   <si>
+    <t xml:space="preserve">Arbeidsmiljøloven § 14-5: skriftlig arbeidsavtale snarest mulig og senest sju dager etter at arbeidsforholdet begynte, når det varer mer enn én måned (endret 1.7.2024; boka skriver én måned, 20.3.4). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hva er minste overtidslønn per time for montøren? Timelønn er 560 000 / 1 800. Loven krever minst 40 % tillegg, allmenngjøringen for elektrofagene 50 %; den høyeste gjelder. To desimaler.</t>
   </si>
   <si>
+    <t xml:space="preserve">Timelønn = årslønn / betalte timer. Overtidslønn = timelønn × (1 + tillegg). Aml § 10-6 (minst 40 %) og allmenngjøringen for elektrofagene (50 %) står ikke i boka; de er hentet fra Arbeidstilsynet. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mye får montøren i feriepenger for et helt opptjeningsår med Fjells avtalte 12 % av 560 000 kr? Hvor mye ville det vært etter ferieloven (10,2 %)?</t>
   </si>
   <si>
+    <t xml:space="preserve">Feriepenger = feriepengegrunnlag × sats. Ferieloven § 10 (10,2 %) står ikke i boka; 12 % ved avtalt femte ferieuke er Fjells avtale, som i OK03. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Gå gjennom punktene i Monas utkast. Ja eller nei: er punktet lovlig? Begrunn med paragraf.</t>
   </si>
   <si>
@@ -447,6 +522,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Mona vurderer å la de to montørene ta 300 overtidstimer hver i året i stedet for å ansette den tredje. Er det lovlig, og hva sier etikken? Tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aml § 10-6 (overtid: særlig og tidsavgrenset behov, 200 timer uten avtale; ikke i boka), § 4-1 (fullt forsvarlig arbeidsmiljø, 20.3.1) og bokas eksempel om for lav bemanning (20.6). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sju dager, og tallene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frist: oppstart + 7 dager. Timelønn: årslønn delt på betalte timer. Overtid: ganger 1,4 etter loven, 1,5 etter allmenngjøringen; den høyeste gjelder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gammel mal, ny lov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sjekk hvert punkt mot § 10-4 (40 timer), § 10-6 (tillegg), § 14-8 (samme dag), § 15-6 (prøvetid inntil 6 mnd) og § 15-3 (én måned).</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.3.4–20.3.7 (aml. §§ 14-5, 14-6, 14-8 og 14-9, med gjeldende rett fra 1.7.2024). Arbeidstid, overtid og ferie står ikke i boka: aml. §§ 10-4 og 10-6, ferieloven § 10, og forskrift om delvis allmenngjøring av Landsoverenskomsten for elektrofagene (Arbeidstilsynet). Lønn og timer: OK02 og OL13. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -460,7 +550,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,8 +617,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -549,8 +661,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -603,7 +733,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -652,11 +782,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -676,11 +826,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -713,8 +863,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -728,7 +878,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -742,7 +892,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1045,7 +1195,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1219,33 +1369,18 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(17.5))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="B18" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
@@ -1255,137 +1390,228 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="F20" s="10"/>
+      <c r="G20" s="11" t="str">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(17.5))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="11" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="14"/>
       <c r="G25" s="11" t="str">
         <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="F26" s="14"/>
+      <c r="G26" s="11" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1398,18 +1624,24 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1426,7 +1658,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1437,7 +1669,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1447,7 +1679,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1458,7 +1690,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1482,10 +1714,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1495,10 +1727,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1508,10 +1740,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1521,10 +1753,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1534,10 +1766,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1547,10 +1779,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1563,7 +1795,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1588,7 +1820,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1600,43 +1832,28 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(17800))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="14"/>
       <c r="G20" s="11" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1644,64 +1861,155 @@
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11" t="str">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(17800))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>84</v>
+      </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="11" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="25">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1714,13 +2022,19 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1737,7 +2051,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1748,7 +2062,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1758,7 +2072,7 @@
     </row>
     <row r="4" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1769,7 +2083,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1779,86 +2093,86 @@
       <c r="G5" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>82</v>
+      <c r="A7" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>85</v>
+      <c r="A8" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="19"/>
+      <c r="A9" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="17"/>
+      <c r="A10" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>92</v>
+      <c r="A11" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="17"/>
+      <c r="A12" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="19"/>
+      <c r="A13" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="17"/>
+      <c r="A14" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1884,7 +2198,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1896,80 +2210,65 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="14"/>
       <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="14"/>
       <c r="G24" s="11" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1977,113 +2276,190 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="14"/>
       <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="14"/>
       <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="14"/>
       <c r="G27" s="11" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
@@ -2092,9 +2468,15 @@
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2111,7 +2493,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2122,7 +2504,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2132,7 +2514,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2143,7 +2525,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2167,10 +2549,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2180,10 +2562,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2193,10 +2575,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2206,10 +2588,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2219,10 +2601,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2232,10 +2614,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2245,10 +2627,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2258,10 +2640,10 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2286,7 +2668,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2298,173 +2680,262 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(466.67))&lt;=0.01,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(67200))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11" t="str">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(466.67))&lt;=0.01,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="10"/>
       <c r="G24" s="11" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F24="","",IF(ABS(F24-(67200))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+    </row>
+    <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="32" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="11" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="11" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="11" t="str">
+        <f aca="false">IF(F32="","",IF(UPPER(TRIM(F32))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="44" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="32">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2478,18 +2949,25 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B22:G22"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B25:G25"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol20/OL20_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol20/OL20_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Håndverkertjenesteloven gjelder tjenester til forbrukere. Er det gitt prisoverslag, skal prisen ikke overstige det vesentlig, og i alle fall ikke med mer enn 15 prosent (§ 32 andre ledd). Prosenten regnes av overslaget. Ser håndverkeren underveis at prisen blir betydelig høyere enn kunden måtte vente, skal han kontakte forbrukeren (§ 7 andre ledd). Brytes plikten, kan kunden slippe å betale fullt ut. Markedsføringsloven krever at påstander kan dokumenteres når markedsføringen skjer (§ 3), forbyr aggressiv handelspraksis (§ 9) og forbyr å gjøre deltakelse i en trekning betinget av kjøp (§ 18, slik boka gjengir den).</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys skulle bytte sikringsskapet og trekke nye kurser i en enebolig. Kunden er en familie, altså en forbruker. Ida ga et skriftlig prisoverslag på 36 000 kr inkl. mva. Underveis viste det seg at flere kurser måtte trekkes om, innenfor det som var avtalt. Montøren så at timene løp, men ringte ikke kunden. Fakturaen ble 42 300 kr inkl. mva, og kunden sier hun bare betaler 36 000. Samme uke legger Ida fram fire markedsføringstiltak for Kari. Gå fram slik: regn taket etter § 32 andre ledd, regn overskridelsen i prosent av overslaget, finn plikten montøren brøt, og vurder Idas tiltak etter markedsføringsloven.</t>
+    <t xml:space="preserve">Nordlys skulle bytte sikringsskapet og trekke nye kurser i en enebolig. Kunden er en familie, altså en forbruker. Ida ga et skriftlig prisoverslag på 36 000 kr inkludert merverdiavgift. Underveis viste det seg at flere kurser måtte trekkes om, innenfor det som var avtalt. Montøren så at timene løp, men ringte ikke kunden. Fakturaen ble 42 300 kr inkludert merverdiavgift, og kunden sier hun bare betaler 36 000. Samme uke legger Ida fram fire markedsføringstiltak for Kari. Gå fram slik: regn taket etter § 32 andre ledd, regn overskridelsen i prosent av overslaget, finn plikten montøren brøt, og vurder Idas tiltak etter markedsføringsloven.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">Prisoverslag</t>
   </si>
   <si>
-    <t xml:space="preserve">36 000 kr inkl. mva, skriftlig</t>
+    <t xml:space="preserve">36 000 kr inkludert merverdiavgift, skriftlig</t>
   </si>
   <si>
     <t xml:space="preserve">Faktura</t>
   </si>
   <si>
-    <t xml:space="preserve">42 300 kr inkl. mva</t>
+    <t xml:space="preserve">42 300 kr inkludert merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Underveis</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">Kort oppsummert: Boka skiller mellom fire prisformer: bindende fast pris, høyeste pris, prisoverslag og uforpliktende prisantydning. Det er håndverkeren som må godtgjøre hvilken som ble gitt (20.2.4). Et prisoverslag skal ikke overskrides vesentlig, og i alle fall ikke med mer enn 15 % (§ 32 andre ledd). Tilleggsarbeid er arbeid utenfor oppdraget: håndverkeren skal kontakte forbrukeren (§ 9 første ledd), og tilleggsarbeid utført i samsvar med § 9 kan kreves betalt (§ 33).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro selger «ladeboks med installasjon» til boligeiere i Oslo øst for 15 300 kr inkl. mva. Mona skriver tilbudene selv, og har brukt tre formuleringer til tre kunder: kunde 1 fikk «fast pris 15 300 kr», kunde 2 fikk «prisoverslag 15 300 kr», og kunde 3 fikk «ca. 15 000 kr, avhengig av hva vi finner». Hos kunde 1 viser det seg at laderen trenger et nytt vern i sikringsskapet som ikke var med i oppdraget: 2 500 kr inkl. mva. Gå fram slik: regn taket for kunde 2, finn ut hva montøren skal gjøre med vernet, regn hva kunde 1 kan faktureres hvis hun sier ja, og ta stilling til hva 15 %-grensen betyr.</t>
+    <t xml:space="preserve">Fjell Elektro selger «ladeboks med installasjon» til boligeiere i Oslo øst for 15 300 kr inkludert merverdiavgift. Mona skriver tilbudene selv, og har brukt tre formuleringer til tre kunder: kunde 1 fikk «fast pris 15 300 kr», kunde 2 fikk «prisoverslag 15 300 kr», og kunde 3 fikk «ca. 15 000 kr, avhengig av hva vi finner». Hos kunde 1 viser det seg at laderen trenger et nytt vern i sikringsskapet som ikke var med i oppdraget: 2 500 kr inkludert merverdiavgift. Gå fram slik: regn taket for kunde 2, finn ut hva montøren skal gjøre med vernet, regn hva kunde 1 kan faktureres hvis hun sier ja, og ta stilling til hva 15 %-grensen betyr.</t>
   </si>
   <si>
     <t xml:space="preserve">Pakken</t>
   </si>
   <si>
-    <t xml:space="preserve">Ladeboks med installasjon, 15 300 kr inkl. mva</t>
+    <t xml:space="preserve">Ladeboks med installasjon, 15 300 kr inkludert merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Kunde 1</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">Hos kunde 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Nytt vern utenfor oppdraget, 2 500 kr inkl. mva</t>
+    <t xml:space="preserve">Nytt vern utenfor oppdraget, 2 500 kr inkludert merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">§ 9 og § 33</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">b)  Hos kunde 1 finner montøren at laderen trenger et nytt vern i sikringsskapet, utenfor oppdraget. Det er praktisk å gjøre det samtidig. Hva skal han gjøre først etter håndverkertjenesteloven?   A: Montere vernet og legge det på fakturaen; det er praktisk å gjøre samtidig   B: Kontakte kunden før han gjør tilleggsarbeidet (§ 9 første ledd)   C: Ingenting; fast pris betyr at alt nødvendig arbeid er inkludert   (skriv bokstaven)</t>
   </si>
   <si>
-    <t xml:space="preserve">c)  Montøren ringer, og kunde 1 sier ja til vernet. Hva kan Fjell fakturere kunde 1 i alt, inkl. mva? Fast pris for oppdraget pluss tilleggsarbeidet.</t>
+    <t xml:space="preserve">c)  Montøren ringer, og kunde 1 sier ja til vernet. Hva kan Fjell fakturere kunde 1 i alt, inkludert merverdiavgift? Fast pris for oppdraget pluss tilleggsarbeidet.</t>
   </si>
   <si>
     <t xml:space="preserve">Håndverkertjenesteloven § 33: tilleggsarbeid som er godtgjort ikke var omfattet av oppdraget, og som er utført i samsvar med § 9, kan kreves betalt (Organisasjon og ledelse 20.2.5). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">Arbeid utenfor oppdraget er tilleggsarbeid (§ 9). Først telefonen, så verktøyet. Sier kunden ja, kan det kreves betalt i tillegg (§ 33), også ved fast pris.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.2.3–20.2.5 (håndverkertjenesteloven §§ 9, 32 og 33). Pakkeprisen bygger på OK07 og MA06. Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.2.3–20.2.5 (håndverkertjenesteloven §§ 9, 32 og 33). Pakkeprisen bygger på Økonomistyring kap. 7 og Markedsføring kap. 6. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: en oppsigelse som skal holde</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">Er grunnen virksomhetens forhold (nedbemanning) eller arbeidstakerens (pliktbrudd)? Advarsel hører til det siste. Drøfting, skriftlighet og omplassering gjelder alltid.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.3.10–20.3.17 (aml. §§ 15-1, 15-4, 15-5, 15-7, 15-11 og 15-12). Oppsigelsesfristene (§ 15-3) mangler i bokas digitale kopi og er hentet fra Arbeidstilsynet, «Oppsigelse» (hentet 26.09.2026). Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.3.10–20.3.17 (arbeidsmiljøloven §§ 15-1, 15-4, 15-5, 15-7, 15-11 og 15-12). Oppsigelsesfristene (§ 15-3) mangler i bokas digitale kopi og er hentet fra Arbeidstilsynet, «Oppsigelse» (hentet 26.09.2026). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B2 · Fjell Elektro: den første arbeidsavtalen Mona skriver</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">Utkastet sier</t>
   </si>
   <si>
-    <t xml:space="preserve">42 t/uke · overtid uten tillegg · endringer innen 1 mnd</t>
+    <t xml:space="preserve">42 timer per uke · overtid uten tillegg · endringer innen 1 måned</t>
   </si>
   <si>
     <t xml:space="preserve">Utkastet sier også</t>
   </si>
   <si>
-    <t xml:space="preserve">Prøvetid 6 mnd · gjensidig frist 1 mnd</t>
+    <t xml:space="preserve">Prøvetid 6 måneder · gjensidig frist 1 måned</t>
   </si>
   <si>
     <t xml:space="preserve">a)  Montøren begynte 1. august, og avtalen ble signert 20. august. Fristen er sju dager etter oppstart. Hvor mange dager for sent ble avtalen signert?</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">b)  Hva er minste overtidslønn per time for montøren? Timelønn er 560 000 / 1 800. Loven krever minst 40 % tillegg, allmenngjøringen for elektrofagene 50 %; den høyeste gjelder. To desimaler.</t>
   </si>
   <si>
-    <t xml:space="preserve">Timelønn = årslønn / betalte timer. Overtidslønn = timelønn × (1 + tillegg). Aml § 10-6 (minst 40 %) og allmenngjøringen for elektrofagene (50 %) står ikke i boka; de er hentet fra Arbeidstilsynet. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+    <t xml:space="preserve">Timelønn = årslønn / betalte timer. Overtidslønn = timelønn × (1 + tillegg). Arbeidsmiljøloven § 10-6 (minst 40 %) og allmenngjøringen for elektrofagene (50 %) står ikke i boka; de er hentet fra Arbeidstilsynet. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Hvor mye får montøren i feriepenger for et helt opptjeningsår med Fjells avtalte 12 % av 560 000 kr? Hvor mye ville det vært etter ferieloven (10,2 %)?</t>
   </si>
   <si>
-    <t xml:space="preserve">Feriepenger = feriepengegrunnlag × sats. Ferieloven § 10 (10,2 %) står ikke i boka; 12 % ved avtalt femte ferieuke er Fjells avtale, som i OK03. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+    <t xml:space="preserve">Feriepenger = feriepengegrunnlag × sats. Ferieloven § 10 (10,2 %) står ikke i boka; 12 % ved avtalt femte ferieuke er Fjells avtale, som i Økonomistyring kap. 3. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Gå gjennom punktene i Monas utkast. Ja eller nei: er punktet lovlig? Begrunn med paragraf.</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">e)  Mona vurderer å la de to montørene ta 300 overtidstimer hver i året i stedet for å ansette den tredje. Er det lovlig, og hva sier etikken? Tre setninger.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aml § 10-6 (overtid: særlig og tidsavgrenset behov, 200 timer uten avtale; ikke i boka), § 4-1 (fullt forsvarlig arbeidsmiljø, 20.3.1) og bokas eksempel om for lav bemanning (20.6). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+    <t xml:space="preserve">Arbeidsmiljøloven § 10-6 (overtid: særlig og tidsavgrenset behov, 200 timer uten avtale; ikke i boka), § 4-1 (fullt forsvarlig arbeidsmiljø, 20.3.1) og bokas eksempel om for lav bemanning (20.6). Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
   </si>
   <si>
     <t xml:space="preserve">Sju dager, og tallene</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">Gammel mal, ny lov</t>
   </si>
   <si>
-    <t xml:space="preserve">Sjekk hvert punkt mot § 10-4 (40 timer), § 10-6 (tillegg), § 14-8 (samme dag), § 15-6 (prøvetid inntil 6 mnd) og § 15-3 (én måned).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.3.4–20.3.7 (aml. §§ 14-5, 14-6, 14-8 og 14-9, med gjeldende rett fra 1.7.2024). Arbeidstid, overtid og ferie står ikke i boka: aml. §§ 10-4 og 10-6, ferieloven § 10, og forskrift om delvis allmenngjøring av Landsoverenskomsten for elektrofagene (Arbeidstilsynet). Lønn og timer: OK02 og OL13. Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Sjekk hvert punkt mot § 10-4 (40 timer), § 10-6 (tillegg), § 14-8 (samme dag), § 15-6 (prøvetid inntil 6 måneder) og § 15-3 (én måned).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 20, avsnitt 20.3.4–20.3.7 (arbeidsmiljøloven §§ 14-5, 14-6, 14-8 og 14-9, gjeldende fra 1.7.2024). Ikke i boka: arbeidstid og overtid (§§ 10-4 og 10-6), ferie (ferieloven § 10) og forskrift om delvis allmenngjøring av Landsoverenskomsten for elektrofagene (Arbeidstilsynet). Lønn og timer: Økonomistyring kap. 2 og kap. 13. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
 </sst>
 </file>
@@ -2430,7 +2430,7 @@
       <c r="F39" s="18"/>
       <c r="G39" s="18"/>
     </row>
-    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
         <v>133</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
         <v>44</v>
       </c>
@@ -2912,7 +2912,7 @@
       <c r="F42" s="18"/>
       <c r="G42" s="18"/>
     </row>
-    <row r="44" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
         <v>171</v>
       </c>

--- a/pensum/ol20/OL20_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol20/OL20_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="172">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 20: Noen viktige lover (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 20: Noen viktige lover (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>
